--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="475">
   <si>
     <t>N°</t>
   </si>
@@ -6260,7 +6260,9 @@
       <c r="B173" s="25" t="s">
         <v>434</v>
       </c>
-      <c r="C173" s="25"/>
+      <c r="C173" s="25" t="s">
+        <v>8</v>
+      </c>
       <c r="D173" s="28" t="s">
         <v>126</v>
       </c>
@@ -6276,7 +6278,7 @@
       <c r="C174" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D174" s="18" t="s">
+      <c r="D174" s="28" t="s">
         <v>126</v>
       </c>
       <c r="E174" s="17" t="s">

--- a/Permanents-Vacataires-ELT2-2026-2027.xlsx
+++ b/Permanents-Vacataires-ELT2-2026-2027.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Répartiion pour Examen" sheetId="8" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Permanents-Vacataires'!$A$1:$G$175</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Répartiion pour Examen'!$A$1:$D$16</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="479">
   <si>
     <t>N°</t>
   </si>
@@ -1343,6 +1343,18 @@
   </si>
   <si>
     <t>salahbnd31@gmail.com</t>
+  </si>
+  <si>
+    <t>KACHA ARSLANE HATEM</t>
+  </si>
+  <si>
+    <t>arslane.kacha@gmail.com</t>
+  </si>
+  <si>
+    <t>LACHABI ABDELHADI</t>
+  </si>
+  <si>
+    <t>lachabi22@gmail.com</t>
   </si>
   <si>
     <t>CYCLE</t>
@@ -6281,18 +6293,49 @@
       <c r="D174" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E174" s="17" t="s">
+      <c r="E174" s="28" t="s">
         <v>138</v>
       </c>
       <c r="F174" s="19" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="175" spans="1:7">
-      <c r="D175" s="18"/>
-    </row>
-    <row r="176" spans="1:7">
-      <c r="D176" s="18"/>
+    <row r="175" ht="15.75" spans="1:7">
+      <c r="A175" s="24">
+        <v>174</v>
+      </c>
+      <c r="B175" s="25" t="s">
+        <v>437</v>
+      </c>
+      <c r="C175" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D175" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F175" s="19" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="176" ht="15.75" spans="1:7">
+      <c r="B176" s="25" t="s">
+        <v>439</v>
+      </c>
+      <c r="C176" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D176" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="E176" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="F176" s="19" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="177" spans="4:4">
       <c r="D177" s="18"/>
@@ -9247,8 +9290,8 @@
       <c r="D1160" s="18"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G174" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A1:G174">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:G175" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A1:G175">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -9340,202 +9383,202 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:4">
       <c r="A2" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:4">
       <c r="A3" s="8"/>
       <c r="B3" s="5" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:4">
       <c r="A4" s="8"/>
       <c r="B4" s="5" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:4">
       <c r="A5" s="8"/>
       <c r="B5" s="5" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:4">
       <c r="A6" s="8"/>
       <c r="B6" s="5" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:4">
       <c r="A7" s="9" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:4">
       <c r="A8" s="8"/>
       <c r="B8" s="10" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:4">
       <c r="A9" s="11" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:4">
       <c r="A10" s="8"/>
       <c r="B10" s="13" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:4">
       <c r="A11" s="8"/>
       <c r="B11" s="13" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:4">
       <c r="A12" s="8"/>
       <c r="B12" s="13" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" ht="15.75" spans="1:4">
       <c r="A13" s="8"/>
       <c r="B13" s="13" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="14" ht="15.75" spans="1:4">
       <c r="A14" s="8"/>
       <c r="B14" s="13" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="15" ht="15.75" spans="1:4">
       <c r="A15" s="8"/>
       <c r="B15" s="13" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="16" ht="15.75" spans="1:4">
       <c r="A16" s="8"/>
       <c r="B16" s="13" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="656" ht="15.75"/>
